--- a/results/errors/performance_metrics.xlsx
+++ b/results/errors/performance_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,9 +508,7 @@
       <c r="H2" t="n">
         <v>31.31</v>
       </c>
-      <c r="I2" t="n">
-        <v>-51.0706</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -545,9 +543,7 @@
       <c r="H3" t="n">
         <v>30.51</v>
       </c>
-      <c r="I3" t="n">
-        <v>-42.5926</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -582,9 +578,7 @@
       <c r="H4" t="n">
         <v>64.77</v>
       </c>
-      <c r="I4" t="n">
-        <v>-164.7875</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -619,9 +613,7 @@
       <c r="H5" t="n">
         <v>253.3</v>
       </c>
-      <c r="I5" t="n">
-        <v>-339.8002</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -656,9 +648,7 @@
       <c r="H6" t="n">
         <v>26.19</v>
       </c>
-      <c r="I6" t="n">
-        <v>-57.4041</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -693,9 +683,7 @@
       <c r="H7" t="n">
         <v>7.81</v>
       </c>
-      <c r="I7" t="n">
-        <v>-0.6534</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -730,9 +718,7 @@
       <c r="H8" t="n">
         <v>1.89</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -767,9 +753,7 @@
       <c r="H9" t="n">
         <v>38.23</v>
       </c>
-      <c r="I9" t="n">
-        <v>-168.4636</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -804,9 +788,7 @@
       <c r="H10" t="n">
         <v>50.1</v>
       </c>
-      <c r="I10" t="n">
-        <v>-225.8249</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -841,9 +823,7 @@
       <c r="H11" t="n">
         <v>38.51</v>
       </c>
-      <c r="I11" t="n">
-        <v>-180.8749</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -878,9 +858,7 @@
       <c r="H12" t="n">
         <v>7.27</v>
       </c>
-      <c r="I12" t="n">
-        <v>-0.1071</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -915,9 +893,7 @@
       <c r="H13" t="n">
         <v>28.73</v>
       </c>
-      <c r="I13" t="n">
-        <v>-39.1696</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -952,9 +928,7 @@
       <c r="H14" t="n">
         <v>12.2</v>
       </c>
-      <c r="I14" t="n">
-        <v>-6.0284</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -989,9 +963,7 @@
       <c r="H15" t="n">
         <v>30.84</v>
       </c>
-      <c r="I15" t="n">
-        <v>-69.2373</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1026,9 +998,7 @@
       <c r="H16" t="n">
         <v>80.34999999999999</v>
       </c>
-      <c r="I16" t="n">
-        <v>-513.3662</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1063,9 +1033,7 @@
       <c r="H17" t="n">
         <v>12.61</v>
       </c>
-      <c r="I17" t="n">
-        <v>-10.5647</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1100,9 +1068,7 @@
       <c r="H18" t="n">
         <v>38.99</v>
       </c>
-      <c r="I18" t="n">
-        <v>-0.1834</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1137,9 +1103,7 @@
       <c r="H19" t="n">
         <v>39.16</v>
       </c>
-      <c r="I19" t="n">
-        <v>-55.4019</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1174,9 +1138,7 @@
       <c r="H20" t="n">
         <v>5.71</v>
       </c>
-      <c r="I20" t="n">
-        <v>-1.8432</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1211,9 +1173,7 @@
       <c r="H21" t="n">
         <v>10.44</v>
       </c>
-      <c r="I21" t="n">
-        <v>-85.3492</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1248,9 +1208,7 @@
       <c r="H22" t="n">
         <v>10.62</v>
       </c>
-      <c r="I22" t="n">
-        <v>-88.22790000000001</v>
-      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1285,9 +1243,7 @@
       <c r="H23" t="n">
         <v>50.99</v>
       </c>
-      <c r="I23" t="n">
-        <v>-73.9014</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1322,9 +1278,7 @@
       <c r="H24" t="n">
         <v>6.83</v>
       </c>
-      <c r="I24" t="n">
-        <v>-3.6853</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1359,9 +1313,7 @@
       <c r="H25" t="n">
         <v>19.21</v>
       </c>
-      <c r="I25" t="n">
-        <v>-14.5044</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1396,9 +1348,7 @@
       <c r="H26" t="n">
         <v>8.17</v>
       </c>
-      <c r="I26" t="n">
-        <v>-2.9505</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1433,9 +1383,7 @@
       <c r="H27" t="n">
         <v>15.95</v>
       </c>
-      <c r="I27" t="n">
-        <v>-17.3275</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1470,8 +1418,7944 @@
       <c r="H28" t="n">
         <v>85.67</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:14:10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.00312042236328125</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1436498.0721</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1190930.0923</v>
+      </c>
+      <c r="H29" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:14:17</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0004792213439941406</v>
+      </c>
+      <c r="F30" t="n">
+        <v>393.9545</v>
+      </c>
+      <c r="G30" t="n">
+        <v>357.1769</v>
+      </c>
+      <c r="H30" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:14:24</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>14.5232</v>
+      </c>
+      <c r="G31" t="n">
+        <v>13.6969</v>
+      </c>
+      <c r="H31" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:14:30</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1264</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:14:37</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.1778</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:14:43</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.1912</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:14:50</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.002201318740844727</v>
+      </c>
+      <c r="F35" t="n">
+        <v>94.2989</v>
+      </c>
+      <c r="G35" t="n">
+        <v>79.7722</v>
+      </c>
+      <c r="H35" t="n">
+        <v>56.77</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:14:57</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.003840208053588867</v>
+      </c>
+      <c r="F36" t="n">
+        <v>9.2248</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8.5312</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:15:04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.001522064208984375</v>
+      </c>
+      <c r="F37" t="n">
+        <v>11.6115</v>
+      </c>
+      <c r="G37" t="n">
+        <v>11.0023</v>
+      </c>
+      <c r="H37" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:15:12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.001000404357910156</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.8138</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.7279</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:15:19</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.001312732696533203</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2406.4564</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2152.4</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:15:26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.00467991828918457</v>
+      </c>
+      <c r="F40" t="n">
+        <v>308162.6735</v>
+      </c>
+      <c r="G40" t="n">
+        <v>245252</v>
+      </c>
+      <c r="H40" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="I40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:15:33</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>7.4481</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6.4846</v>
+      </c>
+      <c r="H41" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="I41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:15:41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.001055717468261719</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.7302999999999999</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.6142</v>
+      </c>
+      <c r="H42" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="I42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:15:48</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.001756906509399414</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1525580.2843</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1289489.2308</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="I43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:15:55</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.3061</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="H44" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-01-14 10:16:03</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.002019405364990234</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.1609</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="H45" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:38:40</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.4602</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.0509</v>
+      </c>
+      <c r="H46" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="I46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:38:51</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>13902.9366</v>
+      </c>
+      <c r="G47" t="n">
+        <v>12483.7439</v>
+      </c>
+      <c r="H47" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="I47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:39:03</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.002199172973632812</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="H48" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:39:15</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.001093864440917969</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="H49" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="I49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:39:28</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.0521</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="I50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:39:41</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.002015352249145508</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4856597350.0927</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3487429735.9786</v>
+      </c>
+      <c r="H51" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="I51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:39:54</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5.4528</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5.3054</v>
+      </c>
+      <c r="H52" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="I52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:40:06</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.7489</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="I53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:40:18</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.001331806182861328</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="H54" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="I54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:40:30</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>season_length=1</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>645591.7498</v>
+      </c>
+      <c r="G55" t="n">
+        <v>614947.7692</v>
+      </c>
+      <c r="H55" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="I55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:40:32</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>13.9339</v>
+      </c>
+      <c r="G56" t="n">
+        <v>13.7994</v>
+      </c>
+      <c r="H56" t="n">
+        <v>31.31</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-51.0706</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:40:36</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.4602</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.0509</v>
+      </c>
+      <c r="H57" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-2.211</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:40:40</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.002011537551879883</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4.1042</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3.6851</v>
+      </c>
+      <c r="H58" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-3.5175</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:40:44</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>40403.5215</v>
+      </c>
+      <c r="G59" t="n">
+        <v>39937.4106</v>
+      </c>
+      <c r="H59" t="n">
+        <v>30.51</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-42.5926</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:40:48</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>13902.9366</v>
+      </c>
+      <c r="G60" t="n">
+        <v>12483.7439</v>
+      </c>
+      <c r="H60" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-4.1616</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:40:51</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>12405.4799</v>
+      </c>
+      <c r="G61" t="n">
+        <v>10852.8208</v>
+      </c>
+      <c r="H61" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-3.1096</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:40:55</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.4537</v>
+      </c>
+      <c r="H62" t="n">
+        <v>64.77</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-164.7875</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:40:59</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="H63" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-0.5626</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:41:03</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.00178980827331543</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="H64" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I64" t="n">
+        <v>-0.5296</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:41:06</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.003460407257080078</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4.9097</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4.9025</v>
+      </c>
+      <c r="H65" t="n">
+        <v>253.3</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-339.8002</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:41:11</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.002290487289428711</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="H66" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-1.7224</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:41:16</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.002017974853515625</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="H67" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-0.8735000000000001</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:41:20</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.008130550384521484</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.4963</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.4921</v>
+      </c>
+      <c r="H68" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-57.4041</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:41:25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.00110316276550293</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.0521</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-0.0048</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:41:30</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.002032279968261719</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.0832</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="I70" t="n">
+        <v>-0.6428</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:41:34</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>4734567566.3351</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3405777542.6699</v>
+      </c>
+      <c r="H71" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="I71" t="n">
+        <v>-0.6534</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:41:39</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.002010583877563477</v>
+      </c>
+      <c r="F72" t="n">
+        <v>4856597350.0927</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3487429735.9786</v>
+      </c>
+      <c r="H72" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-0.7397</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:41:44</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>5395313708.0606</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4252443659.8579</v>
+      </c>
+      <c r="H73" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="I73" t="n">
+        <v>-1.1471</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:41:48</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.2596</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.9103</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:41:53</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.00762486457824707</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.4528</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5.3054</v>
+      </c>
+      <c r="H75" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="I75" t="n">
+        <v>-17.7408</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:41:57</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.0006618499755859375</v>
+      </c>
+      <c r="F76" t="n">
+        <v>15.2945</v>
+      </c>
+      <c r="G76" t="n">
+        <v>12.8359</v>
+      </c>
+      <c r="H76" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="I76" t="n">
+        <v>-146.4386</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:42:01</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>8.907999999999999</v>
+      </c>
+      <c r="G77" t="n">
+        <v>8.8817</v>
+      </c>
+      <c r="H77" t="n">
+        <v>38.23</v>
+      </c>
+      <c r="I77" t="n">
+        <v>-168.4636</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:42:05</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.7489</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="I78" t="n">
+        <v>-0.1977</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:42:10</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.001050233840942383</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1.5051</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1.2708</v>
+      </c>
+      <c r="H79" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="I79" t="n">
+        <v>-3.8377</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:42:15</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.001082420349121094</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="H80" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-225.8249</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:42:20</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.006859779357910156</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="H81" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="I81" t="n">
+        <v>-9.477499999999999</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:42:25</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.007775783538818359</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="H82" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-7.3886</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:42:29</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.00322723388671875</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2650557.0734</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2643260.2692</v>
+      </c>
+      <c r="H83" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="I83" t="n">
+        <v>-180.8749</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:42:33</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.00175166130065918</v>
+      </c>
+      <c r="F84" t="n">
+        <v>645591.7498</v>
+      </c>
+      <c r="G84" t="n">
+        <v>614947.7692</v>
+      </c>
+      <c r="H84" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="I84" t="n">
+        <v>-9.7898</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:42:38</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.003082752227783203</v>
+      </c>
+      <c r="F85" t="n">
+        <v>524504.0886</v>
+      </c>
+      <c r="G85" t="n">
+        <v>467409.3077</v>
+      </c>
+      <c r="H85" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-6.1219</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:42:42</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1491122.479</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1208538.0295</v>
+      </c>
+      <c r="H86" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="I86" t="n">
+        <v>-0.1071</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:42:46</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1436498.0721</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1190930.0923</v>
+      </c>
+      <c r="H87" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="I87" t="n">
+        <v>-0.0275</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:42:51</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.002022504806518555</v>
+      </c>
+      <c r="F88" t="n">
+        <v>3141168.7548</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2591144.6923</v>
+      </c>
+      <c r="H88" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="I88" t="n">
+        <v>-3.9129</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:42:55</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1577.677</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1557.9155</v>
+      </c>
+      <c r="H89" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="I89" t="n">
+        <v>-39.1696</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:42:59</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>393.9545</v>
+      </c>
+      <c r="G90" t="n">
+        <v>357.1769</v>
+      </c>
+      <c r="H90" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="I90" t="n">
+        <v>-1.5047</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:43:04</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0.001934528350830078</v>
+      </c>
+      <c r="F91" t="n">
+        <v>304.9725</v>
+      </c>
+      <c r="G91" t="n">
+        <v>282.6154</v>
+      </c>
+      <c r="H91" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="I91" t="n">
+        <v>-0.501</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:43:08</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>12.802</v>
+      </c>
+      <c r="G92" t="n">
+        <v>11.8563</v>
+      </c>
+      <c r="H92" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I92" t="n">
+        <v>-6.0284</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:43:12</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0.001121282577514648</v>
+      </c>
+      <c r="F93" t="n">
+        <v>14.5232</v>
+      </c>
+      <c r="G93" t="n">
+        <v>13.6969</v>
+      </c>
+      <c r="H93" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="I93" t="n">
+        <v>-8.045400000000001</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:43:17</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>12.8086</v>
+      </c>
+      <c r="G94" t="n">
+        <v>11.6754</v>
+      </c>
+      <c r="H94" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="I94" t="n">
+        <v>-6.0357</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:43:21</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.001146078109741211</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1.1843</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1.1758</v>
+      </c>
+      <c r="H95" t="n">
+        <v>30.84</v>
+      </c>
+      <c r="I95" t="n">
+        <v>-69.2373</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:43:25</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0.001761436462402344</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.1264</v>
+      </c>
+      <c r="H96" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="I96" t="n">
+        <v>-0.1232</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:43:29</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.002020597457885742</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.1834</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.1334</v>
+      </c>
+      <c r="H97" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I97" t="n">
+        <v>-0.6845</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:43:33</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.002014636993408203</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.8927</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1.8909</v>
+      </c>
+      <c r="H98" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I98" t="n">
+        <v>-513.3662</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:43:37</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0.001081466674804688</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.1778</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="H99" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="I99" t="n">
+        <v>-3.5392</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:43:42</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.002950668334960938</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.1257</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="H100" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="I100" t="n">
+        <v>-1.2669</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:43:46</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.004058599472045898</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.6382</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H101" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="I101" t="n">
+        <v>-10.5647</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:43:50</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.1912</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="H102" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I102" t="n">
+        <v>-0.0381</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:43:55</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.004329919815063477</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.2354</v>
+      </c>
+      <c r="H103" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="I103" t="n">
+        <v>-1.7921</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:43:59</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>89.9853</v>
+      </c>
+      <c r="G104" t="n">
+        <v>74.8262</v>
+      </c>
+      <c r="H104" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="I104" t="n">
+        <v>-0.1834</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:44:03</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.003046751022338867</v>
+      </c>
+      <c r="F105" t="n">
+        <v>94.2989</v>
+      </c>
+      <c r="G105" t="n">
+        <v>79.7722</v>
+      </c>
+      <c r="H105" t="n">
+        <v>56.77</v>
+      </c>
+      <c r="I105" t="n">
+        <v>-0.2996</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:44:08</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0.004856348037719727</v>
+      </c>
+      <c r="F106" t="n">
+        <v>427.1589</v>
+      </c>
+      <c r="G106" t="n">
+        <v>303.6266</v>
+      </c>
+      <c r="H106" t="n">
+        <v>193.49</v>
+      </c>
+      <c r="I106" t="n">
+        <v>-25.6674</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:44:12</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.00201416015625</v>
+      </c>
+      <c r="F107" t="n">
+        <v>49.5005</v>
+      </c>
+      <c r="G107" t="n">
+        <v>49.0597</v>
+      </c>
+      <c r="H107" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="I107" t="n">
+        <v>-55.4019</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:44:16</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>9.2248</v>
+      </c>
+      <c r="G108" t="n">
+        <v>8.5312</v>
+      </c>
+      <c r="H108" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="I108" t="n">
+        <v>-0.9588</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:44:20</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>41.6041</v>
+      </c>
+      <c r="G109" t="n">
+        <v>31.7246</v>
+      </c>
+      <c r="H109" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="I109" t="n">
+        <v>-38.8426</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:44:25</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0.00107884407043457</v>
+      </c>
+      <c r="F110" t="n">
+        <v>6.2587</v>
+      </c>
+      <c r="G110" t="n">
+        <v>5.671</v>
+      </c>
+      <c r="H110" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="I110" t="n">
+        <v>-1.8432</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:44:29</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>11.6115</v>
+      </c>
+      <c r="G111" t="n">
+        <v>11.0023</v>
+      </c>
+      <c r="H111" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="I111" t="n">
+        <v>-8.7866</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:44:33</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>10.7881</v>
+      </c>
+      <c r="G112" t="n">
+        <v>9.967700000000001</v>
+      </c>
+      <c r="H112" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I112" t="n">
+        <v>-7.4478</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:44:37</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0.002026081085205078</v>
+      </c>
+      <c r="F113" t="n">
+        <v>3.3816</v>
+      </c>
+      <c r="G113" t="n">
+        <v>3.3619</v>
+      </c>
+      <c r="H113" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="I113" t="n">
+        <v>-85.3492</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:44:42</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0.002015352249145508</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.8138</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.7279</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I114" t="n">
+        <v>-4.0007</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:44:46</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.002022027969360352</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.0108</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.9358</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I115" t="n">
+        <v>-6.7152</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:44:50</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0.002020120620727539</v>
+      </c>
+      <c r="F116" t="n">
+        <v>10165.8396</v>
+      </c>
+      <c r="G116" t="n">
+        <v>10108.7135</v>
+      </c>
+      <c r="H116" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="I116" t="n">
+        <v>-88.22790000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:44:54</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0.00610661506652832</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2406.4564</v>
+      </c>
+      <c r="G117" t="n">
+        <v>2152.4</v>
+      </c>
+      <c r="H117" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I117" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:44:59</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0.001530885696411133</v>
+      </c>
+      <c r="F118" t="n">
+        <v>2989.0796</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2767.3486</v>
+      </c>
+      <c r="H118" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I118" t="n">
+        <v>-6.7142</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:45:03</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1645417.9467</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1634397.1444</v>
+      </c>
+      <c r="H119" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="I119" t="n">
+        <v>-73.9014</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:45:07</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0.001276254653930664</v>
+      </c>
+      <c r="F120" t="n">
+        <v>308162.6735</v>
+      </c>
+      <c r="G120" t="n">
+        <v>245252</v>
+      </c>
+      <c r="H120" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="I120" t="n">
+        <v>-1.6272</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:45:11</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0.001018047332763672</v>
+      </c>
+      <c r="F121" t="n">
+        <v>654800.4427</v>
+      </c>
+      <c r="G121" t="n">
+        <v>590693</v>
+      </c>
+      <c r="H121" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I121" t="n">
+        <v>-10.8619</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:45:16</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0.003004312515258789</v>
+      </c>
+      <c r="F122" t="n">
+        <v>7.9306</v>
+      </c>
+      <c r="G122" t="n">
+        <v>7.2338</v>
+      </c>
+      <c r="H122" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="I122" t="n">
+        <v>-3.6853</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:45:20</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>7.4481</v>
+      </c>
+      <c r="G123" t="n">
+        <v>6.4846</v>
+      </c>
+      <c r="H123" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="I123" t="n">
+        <v>-3.1325</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:45:24</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>8.773</v>
+      </c>
+      <c r="G124" t="n">
+        <v>7.4546</v>
+      </c>
+      <c r="H124" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I124" t="n">
+        <v>-4.7335</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:45:28</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0.002492666244506836</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.5853</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1.5333</v>
+      </c>
+      <c r="H125" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="I125" t="n">
+        <v>-14.5044</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:45:32</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.001399040222167969</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7302999999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.6142</v>
+      </c>
+      <c r="H126" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-2.2905</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:45:37</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.003618717193603516</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.6605</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.5406</v>
+      </c>
+      <c r="H127" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="I127" t="n">
+        <v>-1.6917</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:45:41</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1620364.5486</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1400345.8654</v>
+      </c>
+      <c r="H128" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="I128" t="n">
+        <v>-2.9505</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:45:45</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>0.002017498016357422</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1525580.2843</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1289489.2308</v>
+      </c>
+      <c r="H129" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="I129" t="n">
+        <v>-2.5019</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:45:49</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0.0003893375396728516</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1523806.6185</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1287500.3077</v>
+      </c>
+      <c r="H130" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="I130" t="n">
+        <v>-2.4937</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:45:54</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>0.003055334091186523</v>
+      </c>
+      <c r="F131" t="n">
+        <v>4.7939</v>
+      </c>
+      <c r="G131" t="n">
+        <v>4.6613</v>
+      </c>
+      <c r="H131" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="I131" t="n">
+        <v>-17.3275</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:45:58</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>0.002012491226196289</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2.3061</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="H132" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="I132" t="n">
+        <v>-3.2413</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:46:03</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2.4172</v>
+      </c>
+      <c r="G133" t="n">
+        <v>2.1424</v>
+      </c>
+      <c r="H133" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="I133" t="n">
+        <v>-3.6599</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:46:07</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1.0451</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.9893999999999999</v>
+      </c>
+      <c r="H134" t="n">
+        <v>85.67</v>
+      </c>
+      <c r="I134" t="n">
         <v>-8.6357</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:46:11</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1.1609</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="H135" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-10.8876</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-01-14 14:46:15</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SEASONAL_NAIVE</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1.2736</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1.2309</v>
+      </c>
+      <c r="H136" t="n">
+        <v>110.74</v>
+      </c>
+      <c r="I136" t="n">
+        <v>-13.3081</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:16</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>13.9339</v>
+      </c>
+      <c r="G137" t="n">
+        <v>13.7994</v>
+      </c>
+      <c r="H137" t="n">
+        <v>31.31</v>
+      </c>
+      <c r="I137" t="n">
+        <v>-51.0706</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:18</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>3.4602</v>
+      </c>
+      <c r="G138" t="n">
+        <v>3.0509</v>
+      </c>
+      <c r="H138" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="I138" t="n">
+        <v>-2.211</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:20</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>0.001229286193847656</v>
+      </c>
+      <c r="F139" t="n">
+        <v>4.1042</v>
+      </c>
+      <c r="G139" t="n">
+        <v>3.6851</v>
+      </c>
+      <c r="H139" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="I139" t="n">
+        <v>-3.5175</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:22</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0.002024412155151367</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1.1819</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.9015</v>
+      </c>
+      <c r="H140" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.6254</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:25</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>40403.5215</v>
+      </c>
+      <c r="G141" t="n">
+        <v>39937.4106</v>
+      </c>
+      <c r="H141" t="n">
+        <v>30.51</v>
+      </c>
+      <c r="I141" t="n">
+        <v>-42.5926</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>13902.9366</v>
+      </c>
+      <c r="G142" t="n">
+        <v>12483.7439</v>
+      </c>
+      <c r="H142" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="I142" t="n">
+        <v>-4.1616</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:28</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>12405.4799</v>
+      </c>
+      <c r="G143" t="n">
+        <v>10852.8208</v>
+      </c>
+      <c r="H143" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="I143" t="n">
+        <v>-3.1096</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:29</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0.0171360969543457</v>
+      </c>
+      <c r="F144" t="n">
+        <v>4065.7179</v>
+      </c>
+      <c r="G144" t="n">
+        <v>3605.7247</v>
+      </c>
+      <c r="H144" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.5586</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:32</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0.0008571147918701172</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.4537</v>
+      </c>
+      <c r="H145" t="n">
+        <v>64.77</v>
+      </c>
+      <c r="I145" t="n">
+        <v>-164.7875</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:33</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="H146" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I146" t="n">
+        <v>-0.5626</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:35</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0.001835823059082031</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="H147" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I147" t="n">
+        <v>-0.5296</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:36</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.2714</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="H148" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="I148" t="n">
+        <v>-57.9686</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:39</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>4.9097</v>
+      </c>
+      <c r="G149" t="n">
+        <v>4.9025</v>
+      </c>
+      <c r="H149" t="n">
+        <v>253.3</v>
+      </c>
+      <c r="I149" t="n">
+        <v>-339.8002</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:41</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>0.002023458480834961</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="H150" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="I150" t="n">
+        <v>-1.7224</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:42</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="H151" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="I151" t="n">
+        <v>-0.8735000000000001</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:44</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0.01154136657714844</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1.8853</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1.6842</v>
+      </c>
+      <c r="H152" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="I152" t="n">
+        <v>-49.2549</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:47</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.4963</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.4921</v>
+      </c>
+      <c r="H153" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="I153" t="n">
+        <v>-57.4041</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:48</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.0521</v>
+      </c>
+      <c r="H154" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="I154" t="n">
+        <v>-0.0048</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:50</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.0832</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="H155" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="I155" t="n">
+        <v>-0.6428</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:51</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>0.002024650573730469</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.2357</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.1859</v>
+      </c>
+      <c r="H156" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="I156" t="n">
+        <v>-12.1697</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:54</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>0.002022027969360352</v>
+      </c>
+      <c r="F157" t="n">
+        <v>4734567566.3351</v>
+      </c>
+      <c r="G157" t="n">
+        <v>3405777542.6699</v>
+      </c>
+      <c r="H157" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="I157" t="n">
+        <v>-0.6534</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:56</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="n">
+        <v>4856597350.0927</v>
+      </c>
+      <c r="G158" t="n">
+        <v>3487429735.9786</v>
+      </c>
+      <c r="H158" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="I158" t="n">
+        <v>-0.7397</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:57</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="n">
+        <v>5395313708.0606</v>
+      </c>
+      <c r="G159" t="n">
+        <v>4252443659.8579</v>
+      </c>
+      <c r="H159" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="I159" t="n">
+        <v>-1.1471</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:02:59</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="n">
+        <v>4902383809.3369</v>
+      </c>
+      <c r="G160" t="n">
+        <v>3517810482.9343</v>
+      </c>
+      <c r="H160" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="I160" t="n">
+        <v>-0.7727000000000001</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:02</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1.2596</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.9103</v>
+      </c>
+      <c r="H161" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:04</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="n">
+        <v>5.4528</v>
+      </c>
+      <c r="G162" t="n">
+        <v>5.3054</v>
+      </c>
+      <c r="H162" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="I162" t="n">
+        <v>-17.7408</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:05</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" t="n">
+        <v>15.2945</v>
+      </c>
+      <c r="G163" t="n">
+        <v>12.8359</v>
+      </c>
+      <c r="H163" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="I163" t="n">
+        <v>-146.4386</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:07</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>0.002435684204101562</v>
+      </c>
+      <c r="F164" t="n">
+        <v>8.2988</v>
+      </c>
+      <c r="G164" t="n">
+        <v>7.9234</v>
+      </c>
+      <c r="H164" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="I164" t="n">
+        <v>-42.4082</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:10</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" t="n">
+        <v>8.907999999999999</v>
+      </c>
+      <c r="G165" t="n">
+        <v>8.8817</v>
+      </c>
+      <c r="H165" t="n">
+        <v>38.23</v>
+      </c>
+      <c r="I165" t="n">
+        <v>-168.4636</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:12</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.7489</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="H166" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="I166" t="n">
+        <v>-0.1977</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:13</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1.5051</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1.2708</v>
+      </c>
+      <c r="H167" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="I167" t="n">
+        <v>-3.8377</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:15</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>0.001756668090820312</v>
+      </c>
+      <c r="F168" t="n">
+        <v>3.2521</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2.6374</v>
+      </c>
+      <c r="H168" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="I168" t="n">
+        <v>-21.586</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:18</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>0.002233028411865234</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="H169" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I169" t="n">
+        <v>-225.8249</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:20</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="H170" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="I170" t="n">
+        <v>-9.477499999999999</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:22</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="H171" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="I171" t="n">
+        <v>-7.3886</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:23</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0.002013206481933594</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="H172" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="I172" t="n">
+        <v>-11.8358</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:26</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" t="n">
+        <v>2650557.0734</v>
+      </c>
+      <c r="G173" t="n">
+        <v>2643260.2692</v>
+      </c>
+      <c r="H173" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="I173" t="n">
+        <v>-180.8749</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:28</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" t="n">
+        <v>645591.7498</v>
+      </c>
+      <c r="G174" t="n">
+        <v>614947.7692</v>
+      </c>
+      <c r="H174" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="I174" t="n">
+        <v>-9.7898</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:30</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" t="n">
+        <v>524504.0886</v>
+      </c>
+      <c r="G175" t="n">
+        <v>467409.3077</v>
+      </c>
+      <c r="H175" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="I175" t="n">
+        <v>-6.1219</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:31</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" t="n">
+        <v>529197.9689</v>
+      </c>
+      <c r="G176" t="n">
+        <v>391628.3355</v>
+      </c>
+      <c r="H176" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I176" t="n">
+        <v>-6.2499</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:35</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>0.002283334732055664</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1491122.479</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1208538.0295</v>
+      </c>
+      <c r="H177" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="I177" t="n">
+        <v>-0.1071</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:36</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>0.001003265380859375</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1436498.0721</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1190930.0923</v>
+      </c>
+      <c r="H178" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="I178" t="n">
+        <v>-0.0275</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:38</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" t="n">
+        <v>3141168.7548</v>
+      </c>
+      <c r="G179" t="n">
+        <v>2591144.6923</v>
+      </c>
+      <c r="H179" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="I179" t="n">
+        <v>-3.9129</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:40</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1851392.3318</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1480704.9417</v>
+      </c>
+      <c r="H180" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="I180" t="n">
+        <v>-0.7067</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:43</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1577.677</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1557.9155</v>
+      </c>
+      <c r="H181" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="I181" t="n">
+        <v>-39.1696</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:45</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" t="n">
+        <v>393.9545</v>
+      </c>
+      <c r="G182" t="n">
+        <v>357.1769</v>
+      </c>
+      <c r="H182" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="I182" t="n">
+        <v>-1.5047</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:47</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>0.005316019058227539</v>
+      </c>
+      <c r="F183" t="n">
+        <v>304.9725</v>
+      </c>
+      <c r="G183" t="n">
+        <v>282.6154</v>
+      </c>
+      <c r="H183" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="I183" t="n">
+        <v>-0.501</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:48</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>0.01045966148376465</v>
+      </c>
+      <c r="F184" t="n">
+        <v>399.9086</v>
+      </c>
+      <c r="G184" t="n">
+        <v>288.708</v>
+      </c>
+      <c r="H184" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="I184" t="n">
+        <v>-1.581</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:52</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" t="n">
+        <v>12.802</v>
+      </c>
+      <c r="G185" t="n">
+        <v>11.8563</v>
+      </c>
+      <c r="H185" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I185" t="n">
+        <v>-6.0284</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:54</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>0.002023458480834961</v>
+      </c>
+      <c r="F186" t="n">
+        <v>14.5232</v>
+      </c>
+      <c r="G186" t="n">
+        <v>13.6969</v>
+      </c>
+      <c r="H186" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="I186" t="n">
+        <v>-8.045400000000001</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:56</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="n">
+        <v>12.8086</v>
+      </c>
+      <c r="G187" t="n">
+        <v>11.6754</v>
+      </c>
+      <c r="H187" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="I187" t="n">
+        <v>-6.0357</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:03:57</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="n">
+        <v>17.6086</v>
+      </c>
+      <c r="G188" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="H188" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="I188" t="n">
+        <v>-12.297</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:01</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>0.009827136993408203</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1.1843</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1.1758</v>
+      </c>
+      <c r="H189" t="n">
+        <v>30.84</v>
+      </c>
+      <c r="I189" t="n">
+        <v>-69.2373</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:02</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.1264</v>
+      </c>
+      <c r="H190" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="I190" t="n">
+        <v>-0.1232</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:05</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0.1834</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.1334</v>
+      </c>
+      <c r="H191" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I191" t="n">
+        <v>-0.6845</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:06</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0.7728</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0.6797</v>
+      </c>
+      <c r="H192" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="I192" t="n">
+        <v>-28.9058</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:10</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1.8927</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1.8909</v>
+      </c>
+      <c r="H193" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="I193" t="n">
+        <v>-513.3662</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:12</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>0.007245540618896484</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0.1778</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="H194" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="I194" t="n">
+        <v>-3.5392</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:13</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0.1257</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="H195" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="I195" t="n">
+        <v>-1.2669</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:15</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0.9676</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0.8461</v>
+      </c>
+      <c r="H196" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="I196" t="n">
+        <v>-133.4317</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:19</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0.6382</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H197" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="I197" t="n">
+        <v>-10.5647</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:21</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>0.00851750373840332</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0.1912</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="H198" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I198" t="n">
+        <v>-0.0381</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:22</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0.2354</v>
+      </c>
+      <c r="H199" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="I199" t="n">
+        <v>-1.7921</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:24</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0.6634</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0.5805</v>
+      </c>
+      <c r="H200" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="I200" t="n">
+        <v>-11.4933</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:28</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>0.001263141632080078</v>
+      </c>
+      <c r="F201" t="n">
+        <v>89.9853</v>
+      </c>
+      <c r="G201" t="n">
+        <v>74.8262</v>
+      </c>
+      <c r="H201" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="I201" t="n">
+        <v>-0.1834</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:30</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>0.003879785537719727</v>
+      </c>
+      <c r="F202" t="n">
+        <v>94.2989</v>
+      </c>
+      <c r="G202" t="n">
+        <v>79.7722</v>
+      </c>
+      <c r="H202" t="n">
+        <v>56.77</v>
+      </c>
+      <c r="I202" t="n">
+        <v>-0.2996</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:32</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" t="n">
+        <v>427.1589</v>
+      </c>
+      <c r="G203" t="n">
+        <v>303.6266</v>
+      </c>
+      <c r="H203" t="n">
+        <v>193.49</v>
+      </c>
+      <c r="I203" t="n">
+        <v>-25.6674</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:34</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" t="n">
+        <v>119.0969</v>
+      </c>
+      <c r="G204" t="n">
+        <v>102.5143</v>
+      </c>
+      <c r="H204" t="n">
+        <v>74.03</v>
+      </c>
+      <c r="I204" t="n">
+        <v>-1.073</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:38</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" t="n">
+        <v>49.5005</v>
+      </c>
+      <c r="G205" t="n">
+        <v>49.0597</v>
+      </c>
+      <c r="H205" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="I205" t="n">
+        <v>-55.4019</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:40</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" t="n">
+        <v>9.2248</v>
+      </c>
+      <c r="G206" t="n">
+        <v>8.5312</v>
+      </c>
+      <c r="H206" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="I206" t="n">
+        <v>-0.9588</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:41</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>0.002145051956176758</v>
+      </c>
+      <c r="F207" t="n">
+        <v>41.6041</v>
+      </c>
+      <c r="G207" t="n">
+        <v>31.7246</v>
+      </c>
+      <c r="H207" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="I207" t="n">
+        <v>-38.8426</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:44</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="n">
+        <v>9.1656</v>
+      </c>
+      <c r="G208" t="n">
+        <v>6.1371</v>
+      </c>
+      <c r="H208" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="I208" t="n">
+        <v>-0.9337</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:47</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>0.01211428642272949</v>
+      </c>
+      <c r="F209" t="n">
+        <v>6.2587</v>
+      </c>
+      <c r="G209" t="n">
+        <v>5.671</v>
+      </c>
+      <c r="H209" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="I209" t="n">
+        <v>-1.8432</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:49</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>0.002015590667724609</v>
+      </c>
+      <c r="F210" t="n">
+        <v>11.6115</v>
+      </c>
+      <c r="G210" t="n">
+        <v>11.0023</v>
+      </c>
+      <c r="H210" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="I210" t="n">
+        <v>-8.7866</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:52</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>0.00375676155090332</v>
+      </c>
+      <c r="F211" t="n">
+        <v>10.7881</v>
+      </c>
+      <c r="G211" t="n">
+        <v>9.967700000000001</v>
+      </c>
+      <c r="H211" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="I211" t="n">
+        <v>-7.4478</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:53</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" t="n">
+        <v>15.754</v>
+      </c>
+      <c r="G212" t="n">
+        <v>14.8071</v>
+      </c>
+      <c r="H212" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="I212" t="n">
+        <v>-17.015</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:57</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" t="n">
+        <v>3.3816</v>
+      </c>
+      <c r="G213" t="n">
+        <v>3.3619</v>
+      </c>
+      <c r="H213" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="I213" t="n">
+        <v>-85.3492</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:04:59</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>0.003971576690673828</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0.8138</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0.7279</v>
+      </c>
+      <c r="H214" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I214" t="n">
+        <v>-4.0007</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:01</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" t="n">
+        <v>1.0108</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0.9358</v>
+      </c>
+      <c r="H215" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I215" t="n">
+        <v>-6.7152</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:03</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0.1939</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0.1734</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0.716</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:07</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>0.001065492630004883</v>
+      </c>
+      <c r="F217" t="n">
+        <v>10165.8396</v>
+      </c>
+      <c r="G217" t="n">
+        <v>10108.7135</v>
+      </c>
+      <c r="H217" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="I217" t="n">
+        <v>-88.22790000000001</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:09</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" t="n">
+        <v>2406.4564</v>
+      </c>
+      <c r="G218" t="n">
+        <v>2152.4</v>
+      </c>
+      <c r="H218" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I218" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:11</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" t="n">
+        <v>2989.0796</v>
+      </c>
+      <c r="G219" t="n">
+        <v>2767.3486</v>
+      </c>
+      <c r="H219" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I219" t="n">
+        <v>-6.7142</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:14</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" t="n">
+        <v>647.7084</v>
+      </c>
+      <c r="G220" t="n">
+        <v>579.328</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0.6378</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:17</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1645417.9467</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1634397.1444</v>
+      </c>
+      <c r="H221" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="I221" t="n">
+        <v>-73.9014</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:19</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" t="n">
+        <v>308162.6735</v>
+      </c>
+      <c r="G222" t="n">
+        <v>245252</v>
+      </c>
+      <c r="H222" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="I222" t="n">
+        <v>-1.6272</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:21</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" t="n">
+        <v>654800.4427</v>
+      </c>
+      <c r="G223" t="n">
+        <v>590693</v>
+      </c>
+      <c r="H223" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I223" t="n">
+        <v>-10.8619</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:23</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" t="n">
+        <v>192172.1281</v>
+      </c>
+      <c r="G224" t="n">
+        <v>181347.2756</v>
+      </c>
+      <c r="H224" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="I224" t="n">
+        <v>-0.0217</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:27</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" t="n">
+        <v>7.9306</v>
+      </c>
+      <c r="G225" t="n">
+        <v>7.2338</v>
+      </c>
+      <c r="H225" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="I225" t="n">
+        <v>-3.6853</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:29</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>0.0107879638671875</v>
+      </c>
+      <c r="F226" t="n">
+        <v>7.4481</v>
+      </c>
+      <c r="G226" t="n">
+        <v>6.4846</v>
+      </c>
+      <c r="H226" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="I226" t="n">
+        <v>-3.1325</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:31</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>0.0007345676422119141</v>
+      </c>
+      <c r="F227" t="n">
+        <v>8.773</v>
+      </c>
+      <c r="G227" t="n">
+        <v>7.4546</v>
+      </c>
+      <c r="H227" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I227" t="n">
+        <v>-4.7335</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:33</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
+      <c r="F228" t="n">
+        <v>13.3388</v>
+      </c>
+      <c r="G228" t="n">
+        <v>12.3077</v>
+      </c>
+      <c r="H228" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="I228" t="n">
+        <v>-12.2542</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:37</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" t="n">
+        <v>1.5853</v>
+      </c>
+      <c r="G229" t="n">
+        <v>1.5333</v>
+      </c>
+      <c r="H229" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="I229" t="n">
+        <v>-14.5044</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:39</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0.7302999999999999</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0.6142</v>
+      </c>
+      <c r="H230" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="I230" t="n">
+        <v>-2.2905</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:42</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0.6605</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0.5406</v>
+      </c>
+      <c r="H231" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="I231" t="n">
+        <v>-1.6917</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:44</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0.6413</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0.5261</v>
+      </c>
+      <c r="H232" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="I232" t="n">
+        <v>-1.5371</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:48</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" t="n">
+        <v>1620364.5486</v>
+      </c>
+      <c r="G233" t="n">
+        <v>1400345.8654</v>
+      </c>
+      <c r="H233" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="I233" t="n">
+        <v>-2.9505</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:50</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>0.002718925476074219</v>
+      </c>
+      <c r="F234" t="n">
+        <v>1525580.2843</v>
+      </c>
+      <c r="G234" t="n">
+        <v>1289489.2308</v>
+      </c>
+      <c r="H234" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="I234" t="n">
+        <v>-2.5019</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:53</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" t="n">
+        <v>1523806.6185</v>
+      </c>
+      <c r="G235" t="n">
+        <v>1287500.3077</v>
+      </c>
+      <c r="H235" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="I235" t="n">
+        <v>-2.4937</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:55</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>0.001367568969726562</v>
+      </c>
+      <c r="F236" t="n">
+        <v>1299449.6779</v>
+      </c>
+      <c r="G236" t="n">
+        <v>1089291.1523</v>
+      </c>
+      <c r="H236" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="I236" t="n">
+        <v>-1.5407</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:05:59</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>0.002419710159301758</v>
+      </c>
+      <c r="F237" t="n">
+        <v>4.7939</v>
+      </c>
+      <c r="G237" t="n">
+        <v>4.6613</v>
+      </c>
+      <c r="H237" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="I237" t="n">
+        <v>-17.3275</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:06:02</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" t="n">
+        <v>2.3061</v>
+      </c>
+      <c r="G238" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="H238" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="I238" t="n">
+        <v>-3.2413</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:06:04</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" t="n">
+        <v>2.4172</v>
+      </c>
+      <c r="G239" t="n">
+        <v>2.1424</v>
+      </c>
+      <c r="H239" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="I239" t="n">
+        <v>-3.6599</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:06:07</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>0.01581978797912598</v>
+      </c>
+      <c r="F240" t="n">
+        <v>0.8931</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0.7693</v>
+      </c>
+      <c r="H240" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0.3639</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:06:11</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>HIST_MEAN</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>0.003489255905151367</v>
+      </c>
+      <c r="F241" t="n">
+        <v>1.0451</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0.9893999999999999</v>
+      </c>
+      <c r="H241" t="n">
+        <v>85.67</v>
+      </c>
+      <c r="I241" t="n">
+        <v>-8.6357</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:06:14</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>NAIVE_LAST</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+      <c r="F242" t="n">
+        <v>1.1609</v>
+      </c>
+      <c r="G242" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="H242" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="I242" t="n">
+        <v>-10.8876</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:06:16</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>SEASONAL</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>0.005425214767456055</v>
+      </c>
+      <c r="F243" t="n">
+        <v>1.2736</v>
+      </c>
+      <c r="G243" t="n">
+        <v>1.2309</v>
+      </c>
+      <c r="H243" t="n">
+        <v>110.74</v>
+      </c>
+      <c r="I243" t="n">
+        <v>-13.3081</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-01-14 16:06:19</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>RW_DRIFT</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>0.008626937866210938</v>
+      </c>
+      <c r="F244" t="n">
+        <v>1.2399</v>
+      </c>
+      <c r="G244" t="n">
+        <v>1.1856</v>
+      </c>
+      <c r="H244" t="n">
+        <v>104</v>
+      </c>
+      <c r="I244" t="n">
+        <v>-12.562</v>
       </c>
     </row>
   </sheetData>

--- a/results/errors/performance_metrics.xlsx
+++ b/results/errors/performance_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I244"/>
+  <dimension ref="A1:I250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9358,6 +9358,228 @@
         <v>-12.562</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-01-15 12:07:48</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>order=(0,1,1)</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>0.09147357940673828</v>
+      </c>
+      <c r="F245" t="n">
+        <v>13904.9921</v>
+      </c>
+      <c r="G245" t="n">
+        <v>12486.0331</v>
+      </c>
+      <c r="H245" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="I245" t="n">
+        <v>-4.1632</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-01-15 12:07:53</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>order=(0,1,2)</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>0.1765816211700439</v>
+      </c>
+      <c r="F246" t="n">
+        <v>13892.272</v>
+      </c>
+      <c r="G246" t="n">
+        <v>12472.6771</v>
+      </c>
+      <c r="H246" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="I246" t="n">
+        <v>-4.1537</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-01-15 12:07:58</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>order=(0,1,1)</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>0.1697642803192139</v>
+      </c>
+      <c r="F247" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0.0338</v>
+      </c>
+      <c r="H247" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="I247" t="n">
+        <v>-0.4887</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-01-15 12:08:04</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>order=(0,1,2)</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>0.5723598003387451</v>
+      </c>
+      <c r="F248" t="n">
+        <v>0.0498</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="H248" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="I248" t="n">
+        <v>-0.9872</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-01-15 12:08:56</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>order=(0,1,1)</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>0.1010117530822754</v>
+      </c>
+      <c r="F249" t="n">
+        <v>3.3449</v>
+      </c>
+      <c r="G249" t="n">
+        <v>2.9324</v>
+      </c>
+      <c r="H249" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="I249" t="n">
+        <v>-2.0006</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-01-15 12:09:01</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>order=(0,1,2)</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>0.1393907070159912</v>
+      </c>
+      <c r="F250" t="n">
+        <v>3.3275</v>
+      </c>
+      <c r="G250" t="n">
+        <v>2.911</v>
+      </c>
+      <c r="H250" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="I250" t="n">
+        <v>-1.9695</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/errors/performance_metrics.xlsx
+++ b/results/errors/performance_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I250"/>
+  <dimension ref="A1:I277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9580,6 +9580,1005 @@
         <v>-1.9695</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:24:41</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>population_percent</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>order=(0, 2, 1)</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>1.350050687789917</v>
+      </c>
+      <c r="F251" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I251" t="n">
+        <v>0.9991</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:24:46</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>population_growth</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>0.8217294216156006</v>
+      </c>
+      <c r="F252" t="n">
+        <v>0.3992</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0.2412</v>
+      </c>
+      <c r="H252" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="I252" t="n">
+        <v>-0.4057</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:24:55</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>population_abs</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>order=(0, 2, 1)</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>0.7770581245422363</v>
+      </c>
+      <c r="F253" t="n">
+        <v>62611.0923</v>
+      </c>
+      <c r="G253" t="n">
+        <v>43952.1937</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I253" t="n">
+        <v>0.9941</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:24:59</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>employment_tot</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>0.6094553470611572</v>
+      </c>
+      <c r="F254" t="n">
+        <v>0.1347</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="H254" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="I254" t="n">
+        <v>0.0907</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:25:03</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>employment_male</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>0.4476840496063232</v>
+      </c>
+      <c r="F255" t="n">
+        <v>0.1878</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="H255" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I255" t="n">
+        <v>-0.0009</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:25:07</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>employment_female</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 2)</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>0.9928114414215088</v>
+      </c>
+      <c r="F256" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0.0997</v>
+      </c>
+      <c r="H256" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="I256" t="n">
+        <v>-0.9058</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:25:14</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>forestarea_percent</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>4.103408098220825</v>
+      </c>
+      <c r="F257" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0.0346</v>
+      </c>
+      <c r="H257" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I257" t="n">
+        <v>0.9901</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:25:19</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>forestarea_abs</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>order=(0, 2, 1)</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>0.2480430603027344</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I258" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:25:23</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>agriland_percent</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>0.9345536231994629</v>
+      </c>
+      <c r="F259" t="n">
+        <v>1.3486</v>
+      </c>
+      <c r="G259" t="n">
+        <v>1.1228</v>
+      </c>
+      <c r="H259" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I259" t="n">
+        <v>0.5123</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:25:27</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>agriland_abs</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>0.8716433048248291</v>
+      </c>
+      <c r="F260" t="n">
+        <v>3869.7052</v>
+      </c>
+      <c r="G260" t="n">
+        <v>3236.5127</v>
+      </c>
+      <c r="H260" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I260" t="n">
+        <v>0.6001</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:25:32</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>arableland_percent</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>1.171097755432129</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0.5546</v>
+      </c>
+      <c r="H261" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="I261" t="n">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:25:42</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>arableland_person</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>6.52536416053772</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="H262" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I262" t="n">
+        <v>-0.2779</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:25:46</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>arableland_abs</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>0.3649489879608154</v>
+      </c>
+      <c r="F263" t="n">
+        <v>243931.5384</v>
+      </c>
+      <c r="G263" t="n">
+        <v>188312.1992</v>
+      </c>
+      <c r="H263" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I263" t="n">
+        <v>-0.5404</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:25:50</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>cerealland_abs</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>0.4378013610839844</v>
+      </c>
+      <c r="F264" t="n">
+        <v>59477.5436</v>
+      </c>
+      <c r="G264" t="n">
+        <v>49967.6466</v>
+      </c>
+      <c r="H264" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0.9021</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:25:54</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>cropland_percent</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>0.5767357349395752</v>
+      </c>
+      <c r="F265" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="H265" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="I265" t="n">
+        <v>0.0678</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:25:57</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>withdrawals_percent</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 2)</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>0.5069496631622314</v>
+      </c>
+      <c r="F266" t="n">
+        <v>1.7906</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0.9932</v>
+      </c>
+      <c r="H266" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="I266" t="n">
+        <v>-1.0209</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:26:03</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>fertilizer_abs</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>2.63059401512146</v>
+      </c>
+      <c r="F267" t="n">
+        <v>7.262</v>
+      </c>
+      <c r="G267" t="n">
+        <v>5.6681</v>
+      </c>
+      <c r="H267" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="I267" t="n">
+        <v>-0.2139</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:26:10</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>fertilizer_percent</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 2)</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>1.430130958557129</v>
+      </c>
+      <c r="F268" t="n">
+        <v>70.1455</v>
+      </c>
+      <c r="G268" t="n">
+        <v>57.1741</v>
+      </c>
+      <c r="H268" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0.2809</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:26:15</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>livestock_production_index</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>1.340505123138428</v>
+      </c>
+      <c r="F269" t="n">
+        <v>3.8538</v>
+      </c>
+      <c r="G269" t="n">
+        <v>3.2119</v>
+      </c>
+      <c r="H269" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="I269" t="n">
+        <v>-0.1063</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:26:20</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>food_production_index</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>1.204584836959839</v>
+      </c>
+      <c r="F270" t="n">
+        <v>3.5608</v>
+      </c>
+      <c r="G270" t="n">
+        <v>2.7532</v>
+      </c>
+      <c r="H270" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="I270" t="n">
+        <v>0.07969999999999999</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:26:25</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>crop_production_index</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>2.036657810211182</v>
+      </c>
+      <c r="F271" t="n">
+        <v>4.3529</v>
+      </c>
+      <c r="G271" t="n">
+        <v>3.5195</v>
+      </c>
+      <c r="H271" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="I271" t="n">
+        <v>0.1874</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:26:29</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>cereal_production</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>1.3157639503479</v>
+      </c>
+      <c r="F272" t="n">
+        <v>1058850.3665</v>
+      </c>
+      <c r="G272" t="n">
+        <v>790396.3223</v>
+      </c>
+      <c r="H272" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I272" t="n">
+        <v>0.4418</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:26:37</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>cerealyield_abs</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>3.824667930603027</v>
+      </c>
+      <c r="F273" t="n">
+        <v>319.0638</v>
+      </c>
+      <c r="G273" t="n">
+        <v>247.9097</v>
+      </c>
+      <c r="H273" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="I273" t="n">
+        <v>-0.6429</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:26:43</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>valueadded_percent</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 4)</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>2.050204038619995</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0.0644</v>
+      </c>
+      <c r="H274" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="I274" t="n">
+        <v>-0.3283</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:26:47</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>valueadded_dollars</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>0.1917610168457031</v>
+      </c>
+      <c r="F275" t="n">
+        <v>2728875994.7772</v>
+      </c>
+      <c r="G275" t="n">
+        <v>2246685970.1857</v>
+      </c>
+      <c r="H275" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="I275" t="n">
+        <v>0.4507</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:26:51</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>exports_percent</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 1)</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>0.8959283828735352</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="H276" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="I276" t="n">
+        <v>-0.2137</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-01-17 18:26:57</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>imports_percent</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>order=(0, 1, 3)</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>2.072083950042725</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0.1151</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0.0936</v>
+      </c>
+      <c r="H277" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="I277" t="n">
+        <v>0.8127</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/errors/performance_metrics.xlsx
+++ b/results/errors/performance_metrics.xlsx
@@ -9583,7 +9583,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-01-17 18:24:41</t>
+          <t>2026-01-18 18:06:32</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -9602,7 +9602,7 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1.350050687789917</v>
+        <v>1.30115008354187</v>
       </c>
       <c r="F251" t="n">
         <v>0.0344</v>
@@ -9620,7 +9620,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-01-17 18:24:46</t>
+          <t>2026-01-18 18:06:37</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>0.8217294216156006</v>
+        <v>0.7426013946533203</v>
       </c>
       <c r="F252" t="n">
         <v>0.3992</v>
@@ -9657,7 +9657,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-01-17 18:24:55</t>
+          <t>2026-01-18 18:06:42</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>0.7770581245422363</v>
+        <v>0.622333288192749</v>
       </c>
       <c r="F253" t="n">
         <v>62611.0923</v>
@@ -9694,7 +9694,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-01-17 18:24:59</t>
+          <t>2026-01-18 18:06:46</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>0.6094553470611572</v>
+        <v>0.4831757545471191</v>
       </c>
       <c r="F254" t="n">
         <v>0.1347</v>
@@ -9731,7 +9731,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-01-17 18:25:03</t>
+          <t>2026-01-18 18:06:51</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>0.4476840496063232</v>
+        <v>0.3785011768341064</v>
       </c>
       <c r="F255" t="n">
         <v>0.1878</v>
@@ -9768,7 +9768,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-01-17 18:25:07</t>
+          <t>2026-01-18 18:06:56</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>0.9928114414215088</v>
+        <v>0.8180806636810303</v>
       </c>
       <c r="F256" t="n">
         <v>0.1152</v>
@@ -9805,7 +9805,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-01-17 18:25:14</t>
+          <t>2026-01-18 18:07:03</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -9824,7 +9824,7 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>4.103408098220825</v>
+        <v>3.567748308181763</v>
       </c>
       <c r="F257" t="n">
         <v>0.0361</v>
@@ -9842,7 +9842,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-01-17 18:25:19</t>
+          <t>2026-01-18 18:07:08</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -9861,7 +9861,7 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>0.2480430603027344</v>
+        <v>0.2644731998443604</v>
       </c>
       <c r="F258" t="n">
         <v>0.0076</v>
@@ -9879,7 +9879,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-01-17 18:25:23</t>
+          <t>2026-01-18 18:07:12</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>0.9345536231994629</v>
+        <v>0.8941395282745361</v>
       </c>
       <c r="F259" t="n">
         <v>1.3486</v>
@@ -9916,7 +9916,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2026-01-17 18:25:27</t>
+          <t>2026-01-18 18:07:18</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -9935,7 +9935,7 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>0.8716433048248291</v>
+        <v>0.820324182510376</v>
       </c>
       <c r="F260" t="n">
         <v>3869.7052</v>
@@ -9953,7 +9953,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2026-01-17 18:25:32</t>
+          <t>2026-01-18 18:07:22</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1.171097755432129</v>
+        <v>1.058098077774048</v>
       </c>
       <c r="F261" t="n">
         <v>0.676</v>
@@ -9990,7 +9990,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-01-17 18:25:42</t>
+          <t>2026-01-18 18:07:34</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -10009,7 +10009,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6.52536416053772</v>
+        <v>6.729889392852783</v>
       </c>
       <c r="F262" t="n">
         <v>0.0043</v>
@@ -10027,7 +10027,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-01-17 18:25:46</t>
+          <t>2026-01-18 18:07:39</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -10046,7 +10046,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>0.3649489879608154</v>
+        <v>0.3886504173278809</v>
       </c>
       <c r="F263" t="n">
         <v>243931.5384</v>
@@ -10064,7 +10064,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2026-01-17 18:25:50</t>
+          <t>2026-01-18 18:07:43</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -10083,7 +10083,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>0.4378013610839844</v>
+        <v>0.4391989707946777</v>
       </c>
       <c r="F264" t="n">
         <v>59477.5436</v>
@@ -10101,7 +10101,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2026-01-17 18:25:54</t>
+          <t>2026-01-18 18:07:49</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>0.5767357349395752</v>
+        <v>0.5537505149841309</v>
       </c>
       <c r="F265" t="n">
         <v>0.3887</v>
@@ -10138,7 +10138,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-01-17 18:25:57</t>
+          <t>2026-01-18 18:07:53</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -10157,7 +10157,7 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>0.5069496631622314</v>
+        <v>0.5145764350891113</v>
       </c>
       <c r="F266" t="n">
         <v>1.7906</v>
@@ -10175,7 +10175,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-01-17 18:26:03</t>
+          <t>2026-01-18 18:08:00</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -10194,7 +10194,7 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>2.63059401512146</v>
+        <v>2.36274528503418</v>
       </c>
       <c r="F267" t="n">
         <v>7.262</v>
@@ -10212,7 +10212,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-01-17 18:26:10</t>
+          <t>2026-01-18 18:08:05</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -10231,7 +10231,7 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>1.430130958557129</v>
+        <v>1.331742286682129</v>
       </c>
       <c r="F268" t="n">
         <v>70.1455</v>
@@ -10249,7 +10249,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-01-17 18:26:15</t>
+          <t>2026-01-18 18:08:11</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>1.340505123138428</v>
+        <v>1.097575664520264</v>
       </c>
       <c r="F269" t="n">
         <v>3.8538</v>
@@ -10286,7 +10286,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-01-17 18:26:20</t>
+          <t>2026-01-18 18:08:16</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -10305,7 +10305,7 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>1.204584836959839</v>
+        <v>0.9337112903594971</v>
       </c>
       <c r="F270" t="n">
         <v>3.5608</v>
@@ -10323,7 +10323,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-01-17 18:26:25</t>
+          <t>2026-01-18 18:08:22</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>2.036657810211182</v>
+        <v>1.876446485519409</v>
       </c>
       <c r="F271" t="n">
         <v>4.3529</v>
@@ -10360,7 +10360,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-01-17 18:26:29</t>
+          <t>2026-01-18 18:08:28</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -10379,7 +10379,7 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>1.3157639503479</v>
+        <v>1.282518625259399</v>
       </c>
       <c r="F272" t="n">
         <v>1058850.3665</v>
@@ -10397,7 +10397,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-01-17 18:26:37</t>
+          <t>2026-01-18 18:08:35</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -10416,7 +10416,7 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>3.824667930603027</v>
+        <v>3.179577589035034</v>
       </c>
       <c r="F273" t="n">
         <v>319.0638</v>
@@ -10434,7 +10434,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-01-17 18:26:43</t>
+          <t>2026-01-18 18:08:41</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>2.050204038619995</v>
+        <v>1.77820348739624</v>
       </c>
       <c r="F274" t="n">
         <v>0.07489999999999999</v>
@@ -10471,7 +10471,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2026-01-17 18:26:47</t>
+          <t>2026-01-18 18:08:46</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -10490,7 +10490,7 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>0.1917610168457031</v>
+        <v>0.2134966850280762</v>
       </c>
       <c r="F275" t="n">
         <v>2728875994.7772</v>
@@ -10508,7 +10508,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-01-17 18:26:51</t>
+          <t>2026-01-18 18:08:51</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -10527,7 +10527,7 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>0.8959283828735352</v>
+        <v>0.9240734577178955</v>
       </c>
       <c r="F276" t="n">
         <v>0.0389</v>
@@ -10545,7 +10545,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2026-01-17 18:26:57</t>
+          <t>2026-01-18 18:08:57</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>2.072083950042725</v>
+        <v>1.780628204345703</v>
       </c>
       <c r="F277" t="n">
         <v>0.1151</v>
